--- a/app/dashboard/ingresos_gastos/movimientos.xlsx
+++ b/app/dashboard/ingresos_gastos/movimientos.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\Desktop\MoneyMap\Semana 2 - CdM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\Desktop\MoneyMap\moneymap\app\dashboard\ingresos_gastos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2167029-E4F2-4522-B213-5114C3A68F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7B99A2-0C4D-4457-A68C-C3AD186C2A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movimientos" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Movimientos!$A$1:$N$771</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2422,7 +2425,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2434,6 +2437,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2471,7 +2482,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2481,6 +2492,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2783,7 +2795,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N771"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:N775"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" style="4" bestFit="1" customWidth="1"/>
@@ -2833,7 +2846,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>46142</v>
       </c>
@@ -2874,7 +2887,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>46142</v>
       </c>
@@ -2929,7 +2942,7 @@
         <v>46128</v>
       </c>
       <c r="D4">
-        <v>2822.02</v>
+        <v>1000</v>
       </c>
       <c r="E4">
         <v>5510.23</v>
@@ -2956,7 +2969,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>46139</v>
       </c>
@@ -2997,7 +3010,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>46139</v>
       </c>
@@ -3038,7 +3051,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>46139</v>
       </c>
@@ -3079,7 +3092,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>46134</v>
       </c>
@@ -3120,7 +3133,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>46134</v>
       </c>
@@ -3161,7 +3174,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>46133</v>
       </c>
@@ -3202,7 +3215,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>46132</v>
       </c>
@@ -3243,7 +3256,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>46126</v>
       </c>
@@ -3287,7 +3300,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>46126</v>
       </c>
@@ -3331,7 +3344,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>46125</v>
       </c>
@@ -3375,7 +3388,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>46125</v>
       </c>
@@ -3416,7 +3429,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>46122</v>
       </c>
@@ -3457,7 +3470,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>46122</v>
       </c>
@@ -3495,7 +3508,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>46122</v>
       </c>
@@ -3539,7 +3552,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>46121</v>
       </c>
@@ -3580,7 +3593,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>46121</v>
       </c>
@@ -3624,7 +3637,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>46121</v>
       </c>
@@ -3665,7 +3678,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>46119</v>
       </c>
@@ -3709,7 +3722,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>46118</v>
       </c>
@@ -3750,7 +3763,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>46118</v>
       </c>
@@ -3791,7 +3804,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>46113</v>
       </c>
@@ -3829,7 +3842,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>46113</v>
       </c>
@@ -3873,7 +3886,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>46113</v>
       </c>
@@ -3917,7 +3930,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>46112</v>
       </c>
@@ -3955,7 +3968,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>46112</v>
       </c>
@@ -4010,7 +4023,7 @@
         <v>46097</v>
       </c>
       <c r="D30">
-        <v>2822.33</v>
+        <v>1000</v>
       </c>
       <c r="E30">
         <v>6480.02</v>
@@ -4037,7 +4050,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>46111</v>
       </c>
@@ -4078,7 +4091,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>46111</v>
       </c>
@@ -4119,7 +4132,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>46111</v>
       </c>
@@ -4160,7 +4173,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>46111</v>
       </c>
@@ -4201,7 +4214,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>46107</v>
       </c>
@@ -4242,7 +4255,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>46105</v>
       </c>
@@ -4283,7 +4296,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>46105</v>
       </c>
@@ -4324,7 +4337,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>46105</v>
       </c>
@@ -4365,7 +4378,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>46104</v>
       </c>
@@ -4406,7 +4419,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>46104</v>
       </c>
@@ -4447,7 +4460,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>46104</v>
       </c>
@@ -4488,7 +4501,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>46104</v>
       </c>
@@ -4529,7 +4542,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>46104</v>
       </c>
@@ -4570,7 +4583,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>46104</v>
       </c>
@@ -4611,7 +4624,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>46104</v>
       </c>
@@ -4652,7 +4665,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>46104</v>
       </c>
@@ -4693,7 +4706,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>46101</v>
       </c>
@@ -4734,7 +4747,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>46101</v>
       </c>
@@ -4775,7 +4788,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>46100</v>
       </c>
@@ -4819,7 +4832,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>46099</v>
       </c>
@@ -4860,7 +4873,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>46099</v>
       </c>
@@ -4898,7 +4911,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>46097</v>
       </c>
@@ -4939,7 +4952,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>46093</v>
       </c>
@@ -4983,7 +4996,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>46092</v>
       </c>
@@ -5027,7 +5040,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>46091</v>
       </c>
@@ -5068,7 +5081,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>46091</v>
       </c>
@@ -5106,7 +5119,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>46091</v>
       </c>
@@ -5150,7 +5163,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>46091</v>
       </c>
@@ -5191,7 +5204,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>46091</v>
       </c>
@@ -5232,7 +5245,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>46090</v>
       </c>
@@ -5273,7 +5286,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>46090</v>
       </c>
@@ -5317,7 +5330,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>46090</v>
       </c>
@@ -5358,7 +5371,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>46090</v>
       </c>
@@ -5399,7 +5412,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>46087</v>
       </c>
@@ -5437,7 +5450,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>46087</v>
       </c>
@@ -5481,7 +5494,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>46086</v>
       </c>
@@ -5522,7 +5535,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>46085</v>
       </c>
@@ -5566,7 +5579,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>46085</v>
       </c>
@@ -5610,7 +5623,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>46085</v>
       </c>
@@ -5651,7 +5664,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>46084</v>
       </c>
@@ -5695,7 +5708,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>46083</v>
       </c>
@@ -5736,7 +5749,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>46083</v>
       </c>
@@ -5774,7 +5787,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>46080</v>
       </c>
@@ -5818,7 +5831,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>46079</v>
       </c>
@@ -5859,7 +5872,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>46079</v>
       </c>
@@ -5911,7 +5924,7 @@
         <v>46069</v>
       </c>
       <c r="D76">
-        <v>8740.86</v>
+        <v>1000</v>
       </c>
       <c r="E76">
         <v>12690.33</v>
@@ -5938,7 +5951,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>46078</v>
       </c>
@@ -5979,7 +5992,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>46078</v>
       </c>
@@ -6020,7 +6033,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>46077</v>
       </c>
@@ -6061,7 +6074,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>46076</v>
       </c>
@@ -6102,7 +6115,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>46076</v>
       </c>
@@ -6143,7 +6156,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>46076</v>
       </c>
@@ -6184,7 +6197,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>46076</v>
       </c>
@@ -6225,7 +6238,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>46076</v>
       </c>
@@ -6266,7 +6279,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>46076</v>
       </c>
@@ -6307,7 +6320,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>46069</v>
       </c>
@@ -6348,7 +6361,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>46069</v>
       </c>
@@ -6389,7 +6402,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>46069</v>
       </c>
@@ -6430,7 +6443,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>46066</v>
       </c>
@@ -6474,7 +6487,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>46064</v>
       </c>
@@ -6515,7 +6528,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>46064</v>
       </c>
@@ -6559,7 +6572,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>46063</v>
       </c>
@@ -6600,7 +6613,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>46063</v>
       </c>
@@ -6638,7 +6651,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>46063</v>
       </c>
@@ -6679,7 +6692,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>46063</v>
       </c>
@@ -6720,7 +6733,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>46063</v>
       </c>
@@ -6761,7 +6774,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>46063</v>
       </c>
@@ -6802,7 +6815,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>46059</v>
       </c>
@@ -6843,7 +6856,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>46058</v>
       </c>
@@ -6887,7 +6900,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>46057</v>
       </c>
@@ -6928,7 +6941,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>46057</v>
       </c>
@@ -6972,7 +6985,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>46057</v>
       </c>
@@ -7016,7 +7029,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>46056</v>
       </c>
@@ -7057,7 +7070,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>46056</v>
       </c>
@@ -7101,7 +7114,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>46056</v>
       </c>
@@ -7145,7 +7158,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>46056</v>
       </c>
@@ -7186,7 +7199,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>46056</v>
       </c>
@@ -7227,7 +7240,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>46055</v>
       </c>
@@ -7268,7 +7281,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>46055</v>
       </c>
@@ -7309,7 +7322,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>46055</v>
       </c>
@@ -7350,7 +7363,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>46055</v>
       </c>
@@ -7391,7 +7404,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>46055</v>
       </c>
@@ -7429,7 +7442,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>46055</v>
       </c>
@@ -7470,7 +7483,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>46055</v>
       </c>
@@ -7511,7 +7524,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>46055</v>
       </c>
@@ -7552,7 +7565,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>46052</v>
       </c>
@@ -7596,7 +7609,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>46051</v>
       </c>
@@ -7648,7 +7661,7 @@
         <v>46038</v>
       </c>
       <c r="D118">
-        <v>2827.88</v>
+        <v>1000</v>
       </c>
       <c r="E118">
         <v>6174.06</v>
@@ -7675,7 +7688,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>46051</v>
       </c>
@@ -7719,7 +7732,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>46049</v>
       </c>
@@ -7760,7 +7773,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>46048</v>
       </c>
@@ -7801,7 +7814,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>46048</v>
       </c>
@@ -7842,7 +7855,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>46048</v>
       </c>
@@ -7883,7 +7896,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>46044</v>
       </c>
@@ -7924,7 +7937,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>46041</v>
       </c>
@@ -7965,7 +7978,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>46041</v>
       </c>
@@ -8009,7 +8022,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>46041</v>
       </c>
@@ -8050,7 +8063,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>46041</v>
       </c>
@@ -8091,7 +8104,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>46041</v>
       </c>
@@ -8132,7 +8145,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>46041</v>
       </c>
@@ -8173,7 +8186,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>46041</v>
       </c>
@@ -8214,7 +8227,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>46038</v>
       </c>
@@ -8255,7 +8268,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
         <v>46036</v>
       </c>
@@ -8296,7 +8309,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>46036</v>
       </c>
@@ -8337,7 +8350,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>46036</v>
       </c>
@@ -8378,7 +8391,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>46035</v>
       </c>
@@ -8422,7 +8435,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>46035</v>
       </c>
@@ -8466,7 +8479,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>46034</v>
       </c>
@@ -8504,7 +8517,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>46034</v>
       </c>
@@ -8545,7 +8558,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>46034</v>
       </c>
@@ -8586,7 +8599,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>46034</v>
       </c>
@@ -8627,7 +8640,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>46034</v>
       </c>
@@ -8668,7 +8681,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>46031</v>
       </c>
@@ -8709,7 +8722,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>46031</v>
       </c>
@@ -8750,7 +8763,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>46029</v>
       </c>
@@ -8794,7 +8807,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>46028</v>
       </c>
@@ -8838,7 +8851,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>46027</v>
       </c>
@@ -8879,7 +8892,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>46027</v>
       </c>
@@ -8920,7 +8933,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>46027</v>
       </c>
@@ -8964,7 +8977,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>46027</v>
       </c>
@@ -9008,7 +9021,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>46027</v>
       </c>
@@ -9052,7 +9065,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>46027</v>
       </c>
@@ -9093,7 +9106,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>46027</v>
       </c>
@@ -9134,7 +9147,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>46024</v>
       </c>
@@ -9172,7 +9185,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>46024</v>
       </c>
@@ -9213,7 +9226,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>46022</v>
       </c>
@@ -9251,7 +9264,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
         <v>46022</v>
       </c>
@@ -9292,7 +9305,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>46022</v>
       </c>
@@ -9347,7 +9360,7 @@
         <v>45992</v>
       </c>
       <c r="D159">
-        <v>4893.8</v>
+        <v>1000</v>
       </c>
       <c r="E159">
         <v>7513.71</v>
@@ -9374,7 +9387,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>46020</v>
       </c>
@@ -9415,7 +9428,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>46020</v>
       </c>
@@ -9456,7 +9469,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>46020</v>
       </c>
@@ -9497,7 +9510,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>46017</v>
       </c>
@@ -9538,7 +9551,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>46013</v>
       </c>
@@ -9579,7 +9592,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>46013</v>
       </c>
@@ -9620,7 +9633,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>46013</v>
       </c>
@@ -9661,7 +9674,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>46009</v>
       </c>
@@ -9702,7 +9715,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>46009</v>
       </c>
@@ -9743,7 +9756,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>46009</v>
       </c>
@@ -9784,7 +9797,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>46008</v>
       </c>
@@ -9825,7 +9838,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>46008</v>
       </c>
@@ -9866,7 +9879,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>46008</v>
       </c>
@@ -9907,7 +9920,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>46006</v>
       </c>
@@ -9948,7 +9961,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>46006</v>
       </c>
@@ -9989,7 +10002,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>46006</v>
       </c>
@@ -10030,7 +10043,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>46006</v>
       </c>
@@ -10071,7 +10084,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>46006</v>
       </c>
@@ -10112,7 +10125,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
         <v>46006</v>
       </c>
@@ -10153,7 +10166,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>46006</v>
       </c>
@@ -10194,7 +10207,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="4">
         <v>46006</v>
       </c>
@@ -10235,7 +10248,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>46006</v>
       </c>
@@ -10276,7 +10289,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4">
         <v>46003</v>
       </c>
@@ -10317,7 +10330,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>46002</v>
       </c>
@@ -10361,7 +10374,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>46002</v>
       </c>
@@ -10405,7 +10418,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>46001</v>
       </c>
@@ -10443,7 +10456,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
         <v>45999</v>
       </c>
@@ -10487,7 +10500,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>45996</v>
       </c>
@@ -10531,7 +10544,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
         <v>45996</v>
       </c>
@@ -10575,7 +10588,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>45996</v>
       </c>
@@ -10616,7 +10629,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>45994</v>
       </c>
@@ -10660,7 +10673,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>45994</v>
       </c>
@@ -10704,7 +10717,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>45993</v>
       </c>
@@ -10745,7 +10758,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>45993</v>
       </c>
@@ -10786,7 +10799,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>45992</v>
       </c>
@@ -10824,7 +10837,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>45992</v>
       </c>
@@ -10862,7 +10875,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="4">
         <v>45992</v>
       </c>
@@ -10903,7 +10916,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>45989</v>
       </c>
@@ -10944,7 +10957,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>45989</v>
       </c>
@@ -10985,7 +10998,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>45989</v>
       </c>
@@ -11040,7 +11053,7 @@
         <v>45977</v>
       </c>
       <c r="D200">
-        <v>2773.18</v>
+        <v>1000</v>
       </c>
       <c r="E200">
         <v>6380.26</v>
@@ -11067,7 +11080,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>45985</v>
       </c>
@@ -11108,7 +11121,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
         <v>45985</v>
       </c>
@@ -11149,7 +11162,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>45985</v>
       </c>
@@ -11190,7 +11203,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="4">
         <v>45982</v>
       </c>
@@ -11231,7 +11244,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
         <v>45978</v>
       </c>
@@ -11275,7 +11288,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
         <v>45975</v>
       </c>
@@ -11316,7 +11329,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4">
         <v>45974</v>
       </c>
@@ -11357,7 +11370,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4">
         <v>45973</v>
       </c>
@@ -11398,7 +11411,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>45973</v>
       </c>
@@ -11439,7 +11452,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
         <v>45973</v>
       </c>
@@ -11480,7 +11493,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
         <v>45973</v>
       </c>
@@ -11521,7 +11534,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>45972</v>
       </c>
@@ -11562,7 +11575,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>45972</v>
       </c>
@@ -11603,7 +11616,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4">
         <v>45972</v>
       </c>
@@ -11644,7 +11657,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4">
         <v>45972</v>
       </c>
@@ -11685,7 +11698,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
         <v>45972</v>
       </c>
@@ -11726,7 +11739,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>45972</v>
       </c>
@@ -11767,7 +11780,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
         <v>45971</v>
       </c>
@@ -11808,7 +11821,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
         <v>45971</v>
       </c>
@@ -11849,7 +11862,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4">
         <v>45971</v>
       </c>
@@ -11890,7 +11903,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
         <v>45971</v>
       </c>
@@ -11928,7 +11941,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
         <v>45971</v>
       </c>
@@ -11972,7 +11985,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>45971</v>
       </c>
@@ -12013,7 +12026,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
         <v>45968</v>
       </c>
@@ -12054,7 +12067,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4">
         <v>45968</v>
       </c>
@@ -12095,7 +12108,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
         <v>45967</v>
       </c>
@@ -12139,7 +12152,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="4">
         <v>45966</v>
       </c>
@@ -12177,7 +12190,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4">
         <v>45966</v>
       </c>
@@ -12221,7 +12234,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
         <v>45966</v>
       </c>
@@ -12265,7 +12278,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4">
         <v>45966</v>
       </c>
@@ -12309,7 +12322,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
         <v>45966</v>
       </c>
@@ -12353,7 +12366,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
         <v>45964</v>
       </c>
@@ -12391,7 +12404,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>45964</v>
       </c>
@@ -12435,7 +12448,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
         <v>45964</v>
       </c>
@@ -12476,7 +12489,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
         <v>45961</v>
       </c>
@@ -12517,7 +12530,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4">
         <v>45961</v>
       </c>
@@ -12561,7 +12574,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>45960</v>
       </c>
@@ -12613,7 +12626,7 @@
         <v>45946</v>
       </c>
       <c r="D238">
-        <v>2773.41</v>
+        <v>1000</v>
       </c>
       <c r="E238">
         <v>6389.69</v>
@@ -12640,7 +12653,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>45960</v>
       </c>
@@ -12684,7 +12697,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>45960</v>
       </c>
@@ -12725,7 +12738,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
         <v>45959</v>
       </c>
@@ -12766,7 +12779,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
         <v>45959</v>
       </c>
@@ -12807,7 +12820,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>45957</v>
       </c>
@@ -12848,7 +12861,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4">
         <v>45953</v>
       </c>
@@ -12889,7 +12902,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
         <v>45950</v>
       </c>
@@ -12930,7 +12943,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>45950</v>
       </c>
@@ -12971,7 +12984,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
         <v>45950</v>
       </c>
@@ -13012,7 +13025,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4">
         <v>45950</v>
       </c>
@@ -13053,7 +13066,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>45946</v>
       </c>
@@ -13094,7 +13107,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
         <v>45945</v>
       </c>
@@ -13135,7 +13148,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
         <v>45945</v>
       </c>
@@ -13176,7 +13189,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
         <v>45944</v>
       </c>
@@ -13220,7 +13233,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4">
         <v>45944</v>
       </c>
@@ -13264,7 +13277,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4">
         <v>45944</v>
       </c>
@@ -13305,7 +13318,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
         <v>45943</v>
       </c>
@@ -13346,7 +13359,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4">
         <v>45940</v>
       </c>
@@ -13384,7 +13397,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
         <v>45940</v>
       </c>
@@ -13428,7 +13441,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
         <v>45937</v>
       </c>
@@ -13472,7 +13485,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
         <v>45937</v>
       </c>
@@ -13513,7 +13526,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
         <v>45937</v>
       </c>
@@ -13554,7 +13567,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>45936</v>
       </c>
@@ -13598,7 +13611,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
         <v>45936</v>
       </c>
@@ -13642,7 +13655,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
         <v>45936</v>
       </c>
@@ -13683,7 +13696,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>45933</v>
       </c>
@@ -13727,7 +13740,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>45933</v>
       </c>
@@ -13771,7 +13784,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>45933</v>
       </c>
@@ -13812,7 +13825,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>45931</v>
       </c>
@@ -13853,7 +13866,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
         <v>45931</v>
       </c>
@@ -13894,7 +13907,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
         <v>45931</v>
       </c>
@@ -13938,7 +13951,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
         <v>45931</v>
       </c>
@@ -13976,7 +13989,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4">
         <v>45931</v>
       </c>
@@ -14017,7 +14030,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
         <v>45930</v>
       </c>
@@ -14055,7 +14068,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4">
         <v>45931</v>
       </c>
@@ -14096,7 +14109,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="4">
         <v>45930</v>
       </c>
@@ -14151,7 +14164,7 @@
         <v>45901</v>
       </c>
       <c r="D275">
-        <v>2772.95</v>
+        <v>1000</v>
       </c>
       <c r="E275">
         <v>5888.1</v>
@@ -14178,7 +14191,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4">
         <v>45929</v>
       </c>
@@ -14219,7 +14232,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
         <v>45929</v>
       </c>
@@ -14260,7 +14273,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4">
         <v>45929</v>
       </c>
@@ -14301,7 +14314,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4">
         <v>45929</v>
       </c>
@@ -14342,7 +14355,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4">
         <v>45929</v>
       </c>
@@ -14383,7 +14396,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="4">
         <v>45929</v>
       </c>
@@ -14424,7 +14437,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4">
         <v>45929</v>
       </c>
@@ -14465,7 +14478,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4">
         <v>45926</v>
       </c>
@@ -14506,7 +14519,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4">
         <v>45926</v>
       </c>
@@ -14547,7 +14560,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4">
         <v>45926</v>
       </c>
@@ -14591,7 +14604,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4">
         <v>45923</v>
       </c>
@@ -14632,7 +14645,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="4">
         <v>45923</v>
       </c>
@@ -14676,7 +14689,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4">
         <v>45923</v>
       </c>
@@ -14720,7 +14733,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4">
         <v>45922</v>
       </c>
@@ -14761,7 +14774,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4">
         <v>45922</v>
       </c>
@@ -14802,7 +14815,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4">
         <v>45922</v>
       </c>
@@ -14843,7 +14856,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="4">
         <v>45922</v>
       </c>
@@ -14884,7 +14897,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="4">
         <v>45922</v>
       </c>
@@ -14925,7 +14938,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4">
         <v>45922</v>
       </c>
@@ -14966,7 +14979,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4">
         <v>45922</v>
       </c>
@@ -15007,7 +15020,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4">
         <v>45918</v>
       </c>
@@ -15048,7 +15061,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4">
         <v>45916</v>
       </c>
@@ -15089,7 +15102,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4">
         <v>45915</v>
       </c>
@@ -15130,7 +15143,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4">
         <v>45915</v>
       </c>
@@ -15171,7 +15184,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4">
         <v>45915</v>
       </c>
@@ -15212,7 +15225,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="4">
         <v>45911</v>
       </c>
@@ -15256,7 +15269,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="4">
         <v>45911</v>
       </c>
@@ -15300,7 +15313,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="4">
         <v>45911</v>
       </c>
@@ -15344,7 +15357,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4">
         <v>45910</v>
       </c>
@@ -15382,7 +15395,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4">
         <v>45909</v>
       </c>
@@ -15423,7 +15436,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4">
         <v>45908</v>
       </c>
@@ -15464,7 +15477,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="4">
         <v>45908</v>
       </c>
@@ -15505,7 +15518,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4">
         <v>45908</v>
       </c>
@@ -15549,7 +15562,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="4">
         <v>45908</v>
       </c>
@@ -15590,7 +15603,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4">
         <v>45908</v>
       </c>
@@ -15631,7 +15644,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="4">
         <v>45905</v>
       </c>
@@ -15675,7 +15688,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4">
         <v>45904</v>
       </c>
@@ -15719,7 +15732,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="4">
         <v>45903</v>
       </c>
@@ -15763,7 +15776,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="4">
         <v>45903</v>
       </c>
@@ -15807,7 +15820,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
         <v>45902</v>
       </c>
@@ -15848,7 +15861,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="4">
         <v>45901</v>
       </c>
@@ -15889,7 +15902,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="4">
         <v>45901</v>
       </c>
@@ -15927,7 +15940,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="4">
         <v>45898</v>
       </c>
@@ -15982,7 +15995,7 @@
         <v>45885</v>
       </c>
       <c r="D319">
-        <v>2772.73</v>
+        <v>1000</v>
       </c>
       <c r="E319">
         <v>6545.05</v>
@@ -16009,7 +16022,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="4">
         <v>45894</v>
       </c>
@@ -16050,7 +16063,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="4">
         <v>45889</v>
       </c>
@@ -16091,7 +16104,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="4">
         <v>45883</v>
       </c>
@@ -16132,7 +16145,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="4">
         <v>45883</v>
       </c>
@@ -16173,7 +16186,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="4">
         <v>45883</v>
       </c>
@@ -16214,7 +16227,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="4">
         <v>45883</v>
       </c>
@@ -16255,7 +16268,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="4">
         <v>45882</v>
       </c>
@@ -16293,7 +16306,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="4">
         <v>45882</v>
       </c>
@@ -16334,7 +16347,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="4">
         <v>45881</v>
       </c>
@@ -16378,7 +16391,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="4">
         <v>45880</v>
       </c>
@@ -16419,7 +16432,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="4">
         <v>45880</v>
       </c>
@@ -16457,7 +16470,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="4">
         <v>45880</v>
       </c>
@@ -16501,7 +16514,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="4">
         <v>45880</v>
       </c>
@@ -16542,7 +16555,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="4">
         <v>45880</v>
       </c>
@@ -16583,7 +16596,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="4">
         <v>45880</v>
       </c>
@@ -16624,7 +16637,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="4">
         <v>45880</v>
       </c>
@@ -16665,7 +16678,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="4">
         <v>45880</v>
       </c>
@@ -16706,7 +16719,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="4">
         <v>45880</v>
       </c>
@@ -16747,7 +16760,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="4">
         <v>45880</v>
       </c>
@@ -16788,7 +16801,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="4">
         <v>45877</v>
       </c>
@@ -16829,7 +16842,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="4">
         <v>45877</v>
       </c>
@@ -16870,7 +16883,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="4">
         <v>45877</v>
       </c>
@@ -16911,7 +16924,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4">
         <v>45876</v>
       </c>
@@ -16952,7 +16965,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="4">
         <v>45876</v>
       </c>
@@ -16993,7 +17006,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="4">
         <v>45876</v>
       </c>
@@ -17034,7 +17047,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="4">
         <v>45876</v>
       </c>
@@ -17075,7 +17088,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="4">
         <v>45876</v>
       </c>
@@ -17116,7 +17129,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="4">
         <v>45875</v>
       </c>
@@ -17157,7 +17170,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="4">
         <v>45875</v>
       </c>
@@ -17198,7 +17211,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="4">
         <v>45874</v>
       </c>
@@ -17239,7 +17252,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="4">
         <v>45874</v>
       </c>
@@ -17280,7 +17293,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="4">
         <v>45874</v>
       </c>
@@ -17324,7 +17337,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="4">
         <v>45874</v>
       </c>
@@ -17368,7 +17381,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="4">
         <v>45874</v>
       </c>
@@ -17412,7 +17425,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="4">
         <v>45873</v>
       </c>
@@ -17453,7 +17466,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="4">
         <v>45873</v>
       </c>
@@ -17497,7 +17510,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="4">
         <v>45873</v>
       </c>
@@ -17538,7 +17551,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="4">
         <v>45873</v>
       </c>
@@ -17579,7 +17592,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="4">
         <v>45873</v>
       </c>
@@ -17620,7 +17633,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="4">
         <v>45873</v>
       </c>
@@ -17661,7 +17674,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="4">
         <v>45873</v>
       </c>
@@ -17702,7 +17715,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="4">
         <v>45873</v>
       </c>
@@ -17743,7 +17756,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="4">
         <v>45870</v>
       </c>
@@ -17787,7 +17800,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="4">
         <v>45870</v>
       </c>
@@ -17825,7 +17838,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="4">
         <v>45870</v>
       </c>
@@ -17866,7 +17879,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="4">
         <v>45869</v>
       </c>
@@ -17907,7 +17920,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="4">
         <v>45869</v>
       </c>
@@ -17948,7 +17961,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="4">
         <v>45869</v>
       </c>
@@ -17989,7 +18002,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="4">
         <v>45869</v>
       </c>
@@ -18044,7 +18057,7 @@
         <v>45854</v>
       </c>
       <c r="D369">
-        <v>2821.6</v>
+        <v>1000</v>
       </c>
       <c r="E369">
         <v>5647.06</v>
@@ -18071,7 +18084,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="4">
         <v>45868</v>
       </c>
@@ -18112,7 +18125,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="4">
         <v>45868</v>
       </c>
@@ -18153,7 +18166,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="4">
         <v>45866</v>
       </c>
@@ -18194,7 +18207,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="4">
         <v>45866</v>
       </c>
@@ -18235,7 +18248,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="4">
         <v>45866</v>
       </c>
@@ -18276,7 +18289,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="4">
         <v>45866</v>
       </c>
@@ -18317,7 +18330,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="4">
         <v>45866</v>
       </c>
@@ -18358,7 +18371,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="4">
         <v>45866</v>
       </c>
@@ -18399,7 +18412,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="4">
         <v>45866</v>
       </c>
@@ -18440,7 +18453,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="4">
         <v>45866</v>
       </c>
@@ -18481,7 +18494,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="4">
         <v>45866</v>
       </c>
@@ -18522,7 +18535,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="4">
         <v>45866</v>
       </c>
@@ -18563,7 +18576,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="4">
         <v>45866</v>
       </c>
@@ -18604,7 +18617,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="4">
         <v>45863</v>
       </c>
@@ -18645,7 +18658,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="4">
         <v>45863</v>
       </c>
@@ -18683,7 +18696,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="4">
         <v>45861</v>
       </c>
@@ -18724,7 +18737,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="4">
         <v>45861</v>
       </c>
@@ -18765,7 +18778,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="4">
         <v>45861</v>
       </c>
@@ -18806,7 +18819,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="4">
         <v>45861</v>
       </c>
@@ -18847,7 +18860,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="4">
         <v>45860</v>
       </c>
@@ -18888,7 +18901,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="4">
         <v>45860</v>
       </c>
@@ -18929,7 +18942,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="4">
         <v>45860</v>
       </c>
@@ -18970,7 +18983,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="4">
         <v>45859</v>
       </c>
@@ -19011,7 +19024,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="4">
         <v>45859</v>
       </c>
@@ -19052,7 +19065,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="4">
         <v>45859</v>
       </c>
@@ -19093,7 +19106,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="4">
         <v>45859</v>
       </c>
@@ -19134,7 +19147,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="4">
         <v>45859</v>
       </c>
@@ -19175,7 +19188,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="4">
         <v>45859</v>
       </c>
@@ -19216,7 +19229,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="4">
         <v>45859</v>
       </c>
@@ -19257,7 +19270,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="4">
         <v>45859</v>
       </c>
@@ -19298,7 +19311,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="4">
         <v>45856</v>
       </c>
@@ -19339,7 +19352,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="4">
         <v>45855</v>
       </c>
@@ -19383,7 +19396,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="4">
         <v>45854</v>
       </c>
@@ -19421,7 +19434,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="4">
         <v>45853</v>
       </c>
@@ -19462,7 +19475,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="4">
         <v>45853</v>
       </c>
@@ -19503,7 +19516,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="4">
         <v>45853</v>
       </c>
@@ -19544,7 +19557,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="4">
         <v>45852</v>
       </c>
@@ -19585,7 +19598,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="4">
         <v>45852</v>
       </c>
@@ -19626,7 +19639,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="4">
         <v>45852</v>
       </c>
@@ -19667,7 +19680,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="409" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="4">
         <v>45852</v>
       </c>
@@ -19708,7 +19721,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="4">
         <v>45852</v>
       </c>
@@ -19749,7 +19762,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="4">
         <v>45852</v>
       </c>
@@ -19790,7 +19803,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="4">
         <v>45852</v>
       </c>
@@ -19831,7 +19844,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="4">
         <v>45852</v>
       </c>
@@ -19872,7 +19885,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="4">
         <v>45852</v>
       </c>
@@ -19913,7 +19926,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="4">
         <v>45852</v>
       </c>
@@ -19954,7 +19967,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="4">
         <v>45852</v>
       </c>
@@ -19995,7 +20008,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="4">
         <v>45852</v>
       </c>
@@ -20036,7 +20049,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="4">
         <v>45852</v>
       </c>
@@ -20077,7 +20090,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="4">
         <v>45852</v>
       </c>
@@ -20118,7 +20131,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="4">
         <v>45852</v>
       </c>
@@ -20159,7 +20172,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="4">
         <v>45849</v>
       </c>
@@ -20203,7 +20216,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="4">
         <v>45849</v>
       </c>
@@ -20247,7 +20260,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="4">
         <v>45848</v>
       </c>
@@ -20288,7 +20301,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="4">
         <v>45848</v>
       </c>
@@ -20329,7 +20342,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="4">
         <v>45848</v>
       </c>
@@ -20367,7 +20380,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="4">
         <v>45848</v>
       </c>
@@ -20411,7 +20424,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="4">
         <v>45848</v>
       </c>
@@ -20452,7 +20465,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="4">
         <v>45848</v>
       </c>
@@ -20493,7 +20506,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="4">
         <v>45847</v>
       </c>
@@ -20534,7 +20547,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="4">
         <v>45846</v>
       </c>
@@ -20575,7 +20588,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="4">
         <v>45846</v>
       </c>
@@ -20619,7 +20632,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="4">
         <v>45846</v>
       </c>
@@ -20660,7 +20673,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="4">
         <v>45845</v>
       </c>
@@ -20704,7 +20717,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="4">
         <v>45845</v>
       </c>
@@ -20748,7 +20761,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="4">
         <v>45845</v>
       </c>
@@ -20789,7 +20802,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="4">
         <v>45845</v>
       </c>
@@ -20830,7 +20843,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="4">
         <v>45845</v>
       </c>
@@ -20871,7 +20884,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="438" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="4">
         <v>45845</v>
       </c>
@@ -20912,7 +20925,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="439" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="4">
         <v>45845</v>
       </c>
@@ -20953,7 +20966,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="440" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="4">
         <v>45842</v>
       </c>
@@ -20994,7 +21007,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="441" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="4">
         <v>45842</v>
       </c>
@@ -21035,7 +21048,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="442" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="4">
         <v>45841</v>
       </c>
@@ -21076,7 +21089,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="443" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="4">
         <v>45841</v>
       </c>
@@ -21117,7 +21130,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="444" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="4">
         <v>45841</v>
       </c>
@@ -21161,7 +21174,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="445" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="4">
         <v>45841</v>
       </c>
@@ -21202,7 +21215,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="446" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="4">
         <v>45841</v>
       </c>
@@ -21243,7 +21256,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="447" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="4">
         <v>45841</v>
       </c>
@@ -21284,7 +21297,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="448" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="4">
         <v>45841</v>
       </c>
@@ -21325,7 +21338,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="449" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="4">
         <v>45840</v>
       </c>
@@ -21366,7 +21379,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="450" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="4">
         <v>45840</v>
       </c>
@@ -21407,7 +21420,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="451" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="4">
         <v>45840</v>
       </c>
@@ -21448,7 +21461,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="452" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="4">
         <v>45839</v>
       </c>
@@ -21489,7 +21502,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="453" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="4">
         <v>45839</v>
       </c>
@@ -21530,7 +21543,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="454" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="4">
         <v>45839</v>
       </c>
@@ -21568,7 +21581,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="455" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="4">
         <v>45839</v>
       </c>
@@ -21609,7 +21622,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="456" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="4">
         <v>45838</v>
       </c>
@@ -21647,7 +21660,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="457" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="4">
         <v>45838</v>
       </c>
@@ -21688,7 +21701,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="458" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="4">
         <v>45838</v>
       </c>
@@ -21732,7 +21745,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="459" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="4">
         <v>45838</v>
       </c>
@@ -21770,7 +21783,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="460" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="4">
         <v>45838</v>
       </c>
@@ -21811,7 +21824,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="461" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="4">
         <v>45838</v>
       </c>
@@ -21852,7 +21865,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="462" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="4">
         <v>45838</v>
       </c>
@@ -21893,7 +21906,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="463" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="4">
         <v>45838</v>
       </c>
@@ -21934,7 +21947,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="464" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="4">
         <v>45838</v>
       </c>
@@ -21975,7 +21988,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="465" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="4">
         <v>45838</v>
       </c>
@@ -22016,7 +22029,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="466" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="4">
         <v>45838</v>
       </c>
@@ -22057,7 +22070,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="467" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="4">
         <v>45835</v>
       </c>
@@ -22109,7 +22122,7 @@
         <v>45809</v>
       </c>
       <c r="D468">
-        <v>4724.34</v>
+        <v>1000</v>
       </c>
       <c r="E468">
         <v>7787.73</v>
@@ -22136,7 +22149,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="469" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="4">
         <v>45834</v>
       </c>
@@ -22177,7 +22190,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="470" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="4">
         <v>45834</v>
       </c>
@@ -22215,7 +22228,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="471" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="4">
         <v>45834</v>
       </c>
@@ -22256,7 +22269,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="472" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="4">
         <v>45828</v>
       </c>
@@ -22297,7 +22310,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="473" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="4">
         <v>45827</v>
       </c>
@@ -22338,7 +22351,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="474" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="4">
         <v>45827</v>
       </c>
@@ -22379,7 +22392,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="475" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="4">
         <v>45827</v>
       </c>
@@ -22420,7 +22433,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="476" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="4">
         <v>45827</v>
       </c>
@@ -22461,7 +22474,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="477" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="4">
         <v>45826</v>
       </c>
@@ -22502,7 +22515,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="478" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="4">
         <v>45826</v>
       </c>
@@ -22543,7 +22556,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="479" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="4">
         <v>45826</v>
       </c>
@@ -22584,7 +22597,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="480" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="4">
         <v>45826</v>
       </c>
@@ -22625,7 +22638,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="481" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="4">
         <v>45825</v>
       </c>
@@ -22666,7 +22679,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="482" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="4">
         <v>45824</v>
       </c>
@@ -22707,7 +22720,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="483" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="4">
         <v>45824</v>
       </c>
@@ -22748,7 +22761,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="484" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="4">
         <v>45824</v>
       </c>
@@ -22789,7 +22802,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="485" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="4">
         <v>45824</v>
       </c>
@@ -22830,7 +22843,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="486" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="4">
         <v>45824</v>
       </c>
@@ -22871,7 +22884,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="487" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="4">
         <v>45821</v>
       </c>
@@ -22912,7 +22925,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="488" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="4">
         <v>45821</v>
       </c>
@@ -22953,7 +22966,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="489" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="4">
         <v>45820</v>
       </c>
@@ -22994,7 +23007,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="490" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="4">
         <v>45819</v>
       </c>
@@ -23038,7 +23051,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="491" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="4">
         <v>45819</v>
       </c>
@@ -23079,7 +23092,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="492" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="4">
         <v>45818</v>
       </c>
@@ -23120,7 +23133,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="493" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="4">
         <v>45818</v>
       </c>
@@ -23161,7 +23174,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="494" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="4">
         <v>45818</v>
       </c>
@@ -23199,7 +23212,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="495" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="4">
         <v>45817</v>
       </c>
@@ -23240,7 +23253,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="496" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="4">
         <v>45817</v>
       </c>
@@ -23281,7 +23294,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="497" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="4">
         <v>45817</v>
       </c>
@@ -23322,7 +23335,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="498" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="4">
         <v>45817</v>
       </c>
@@ -23363,7 +23376,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="499" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="4">
         <v>45817</v>
       </c>
@@ -23404,7 +23417,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="500" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="4">
         <v>45817</v>
       </c>
@@ -23445,7 +23458,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="501" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="4">
         <v>45817</v>
       </c>
@@ -23486,7 +23499,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="502" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="4">
         <v>45817</v>
       </c>
@@ -23527,7 +23540,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="503" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="4">
         <v>45814</v>
       </c>
@@ -23568,7 +23581,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="504" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="4">
         <v>45814</v>
       </c>
@@ -23609,7 +23622,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="505" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="4">
         <v>45814</v>
       </c>
@@ -23650,7 +23663,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="506" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="4">
         <v>45814</v>
       </c>
@@ -23691,7 +23704,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="507" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="4">
         <v>45813</v>
       </c>
@@ -23732,7 +23745,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="508" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="4">
         <v>45813</v>
       </c>
@@ -23776,7 +23789,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="509" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="4">
         <v>45812</v>
       </c>
@@ -23817,7 +23830,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="510" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="4">
         <v>45812</v>
       </c>
@@ -23861,7 +23874,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="511" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="4">
         <v>45812</v>
       </c>
@@ -23905,7 +23918,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="512" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="4">
         <v>45811</v>
       </c>
@@ -23946,7 +23959,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="513" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="4">
         <v>45811</v>
       </c>
@@ -23987,7 +24000,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="514" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="4">
         <v>45811</v>
       </c>
@@ -24028,7 +24041,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="515" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="4">
         <v>45811</v>
       </c>
@@ -24069,7 +24082,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="516" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="4">
         <v>45810</v>
       </c>
@@ -24107,7 +24120,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="517" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="4">
         <v>45810</v>
       </c>
@@ -24148,7 +24161,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="518" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="4">
         <v>45810</v>
       </c>
@@ -24189,7 +24202,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="519" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="4">
         <v>45810</v>
       </c>
@@ -24230,7 +24243,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="520" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="4">
         <v>45807</v>
       </c>
@@ -24285,7 +24298,7 @@
         <v>45793</v>
       </c>
       <c r="D521">
-        <v>2771.94</v>
+        <v>1000</v>
       </c>
       <c r="E521">
         <v>5231.79</v>
@@ -24312,7 +24325,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="522" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="4">
         <v>45806</v>
       </c>
@@ -24353,7 +24366,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="523" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="4">
         <v>45805</v>
       </c>
@@ -24394,7 +24407,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="524" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="4">
         <v>45803</v>
       </c>
@@ -24435,7 +24448,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="525" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="4">
         <v>45800</v>
       </c>
@@ -24476,7 +24489,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="526" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="4">
         <v>45800</v>
       </c>
@@ -24517,7 +24530,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="527" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="4">
         <v>45799</v>
       </c>
@@ -24558,7 +24571,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="528" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="4">
         <v>45799</v>
       </c>
@@ -24599,7 +24612,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="529" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="4">
         <v>45798</v>
       </c>
@@ -24640,7 +24653,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="530" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="4">
         <v>45798</v>
       </c>
@@ -24681,7 +24694,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="531" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="4">
         <v>45797</v>
       </c>
@@ -24722,7 +24735,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="532" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="4">
         <v>45796</v>
       </c>
@@ -24763,7 +24776,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="533" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="4">
         <v>45796</v>
       </c>
@@ -24804,7 +24817,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="534" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="4">
         <v>45796</v>
       </c>
@@ -24845,7 +24858,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="535" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="4">
         <v>45796</v>
       </c>
@@ -24886,7 +24899,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="536" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="4">
         <v>45796</v>
       </c>
@@ -24927,7 +24940,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="537" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="4">
         <v>45796</v>
       </c>
@@ -24968,7 +24981,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="538" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="4">
         <v>45796</v>
       </c>
@@ -25009,7 +25022,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="539" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="4">
         <v>45796</v>
       </c>
@@ -25050,7 +25063,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="540" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="4">
         <v>45796</v>
       </c>
@@ -25091,7 +25104,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="541" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="4">
         <v>45796</v>
       </c>
@@ -25132,7 +25145,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="542" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="4">
         <v>45793</v>
       </c>
@@ -25173,7 +25186,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="543" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="4">
         <v>45793</v>
       </c>
@@ -25214,7 +25227,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="544" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="4">
         <v>45792</v>
       </c>
@@ -25255,7 +25268,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="545" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="4">
         <v>45792</v>
       </c>
@@ -25296,7 +25309,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="546" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="4">
         <v>45792</v>
       </c>
@@ -25337,7 +25350,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="547" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="4">
         <v>45791</v>
       </c>
@@ -25378,7 +25391,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="548" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="4">
         <v>45790</v>
       </c>
@@ -25422,7 +25435,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="549" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="4">
         <v>45790</v>
       </c>
@@ -25463,7 +25476,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="550" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="4">
         <v>45790</v>
       </c>
@@ -25504,7 +25517,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="551" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="4">
         <v>45789</v>
       </c>
@@ -25545,7 +25558,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="552" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="4">
         <v>45789</v>
       </c>
@@ -25586,7 +25599,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="553" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="4">
         <v>45789</v>
       </c>
@@ -25624,7 +25637,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="554" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="4">
         <v>45789</v>
       </c>
@@ -25668,7 +25681,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="555" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="4">
         <v>45789</v>
       </c>
@@ -25709,7 +25722,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="556" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="4">
         <v>45789</v>
       </c>
@@ -25750,7 +25763,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="557" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="4">
         <v>45789</v>
       </c>
@@ -25791,7 +25804,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="558" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="4">
         <v>45786</v>
       </c>
@@ -25832,7 +25845,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="559" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="4">
         <v>45786</v>
       </c>
@@ -25873,7 +25886,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="560" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="4">
         <v>45786</v>
       </c>
@@ -25914,7 +25927,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="561" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="4">
         <v>45786</v>
       </c>
@@ -25952,7 +25965,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="562" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="4">
         <v>45786</v>
       </c>
@@ -25993,7 +26006,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="563" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="4">
         <v>45786</v>
       </c>
@@ -26034,7 +26047,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="564" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="4">
         <v>45785</v>
       </c>
@@ -26075,7 +26088,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="565" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="4">
         <v>45785</v>
       </c>
@@ -26116,7 +26129,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="566" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="4">
         <v>45785</v>
       </c>
@@ -26157,7 +26170,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="567" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="4">
         <v>45785</v>
       </c>
@@ -26198,7 +26211,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="568" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="4">
         <v>45785</v>
       </c>
@@ -26239,7 +26252,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="569" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="4">
         <v>45785</v>
       </c>
@@ -26280,7 +26293,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="570" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="4">
         <v>45784</v>
       </c>
@@ -26321,7 +26334,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="571" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="4">
         <v>45784</v>
       </c>
@@ -26362,7 +26375,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="572" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="4">
         <v>45784</v>
       </c>
@@ -26403,7 +26416,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="573" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="4">
         <v>45783</v>
       </c>
@@ -26447,7 +26460,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="574" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="4">
         <v>45783</v>
       </c>
@@ -26491,7 +26504,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="575" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="4">
         <v>45783</v>
       </c>
@@ -26535,7 +26548,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="576" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="4">
         <v>45782</v>
       </c>
@@ -26576,7 +26589,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="577" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="4">
         <v>45782</v>
       </c>
@@ -26617,7 +26630,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="578" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="4">
         <v>45782</v>
       </c>
@@ -26661,7 +26674,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="579" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="4">
         <v>45782</v>
       </c>
@@ -26702,7 +26715,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="580" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="4">
         <v>45782</v>
       </c>
@@ -26743,7 +26756,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="581" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="4">
         <v>45782</v>
       </c>
@@ -26784,7 +26797,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="582" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="4">
         <v>45779</v>
       </c>
@@ -26825,7 +26838,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="583" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="4">
         <v>45779</v>
       </c>
@@ -26863,7 +26876,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="584" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="4">
         <v>45779</v>
       </c>
@@ -26904,7 +26917,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="585" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="4">
         <v>45779</v>
       </c>
@@ -26945,7 +26958,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="586" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="4">
         <v>45779</v>
       </c>
@@ -26986,7 +26999,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="587" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="4">
         <v>45779</v>
       </c>
@@ -27027,7 +27040,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="588" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="4">
         <v>45779</v>
       </c>
@@ -27065,7 +27078,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="589" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="4">
         <v>45779</v>
       </c>
@@ -27106,7 +27119,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="590" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="4">
         <v>45779</v>
       </c>
@@ -27147,7 +27160,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="591" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="4">
         <v>45779</v>
       </c>
@@ -27188,7 +27201,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="592" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="4">
         <v>45779</v>
       </c>
@@ -27229,7 +27242,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="593" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="4">
         <v>45777</v>
       </c>
@@ -27270,7 +27283,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="594" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="4">
         <v>45777</v>
       </c>
@@ -27311,7 +27324,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="595" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="4">
         <v>45777</v>
       </c>
@@ -27352,7 +27365,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="596" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="4">
         <v>45777</v>
       </c>
@@ -27396,7 +27409,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="597" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="4">
         <v>45777</v>
       </c>
@@ -27448,7 +27461,7 @@
         <v>45763</v>
       </c>
       <c r="D598">
-        <v>2773.33</v>
+        <v>1000</v>
       </c>
       <c r="E598">
         <v>7090.24</v>
@@ -27475,7 +27488,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="599" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="4">
         <v>45775</v>
       </c>
@@ -27519,7 +27532,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="600" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="4">
         <v>45775</v>
       </c>
@@ -27560,7 +27573,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="601" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="4">
         <v>45775</v>
       </c>
@@ -27601,7 +27614,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="602" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="4">
         <v>45775</v>
       </c>
@@ -27642,7 +27655,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="603" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" s="4">
         <v>45772</v>
       </c>
@@ -27683,7 +27696,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="604" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" s="4">
         <v>45772</v>
       </c>
@@ -27724,7 +27737,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="605" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" s="4">
         <v>45772</v>
       </c>
@@ -27765,7 +27778,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="606" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" s="4">
         <v>45772</v>
       </c>
@@ -27806,7 +27819,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="607" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" s="4">
         <v>45771</v>
       </c>
@@ -27847,7 +27860,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="608" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" s="4">
         <v>45769</v>
       </c>
@@ -27888,7 +27901,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="609" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" s="4">
         <v>45768</v>
       </c>
@@ -27929,7 +27942,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="610" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" s="4">
         <v>45768</v>
       </c>
@@ -27970,7 +27983,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="611" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="4">
         <v>45768</v>
       </c>
@@ -28011,7 +28024,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="612" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="4">
         <v>45768</v>
       </c>
@@ -28052,7 +28065,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="613" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="4">
         <v>45768</v>
       </c>
@@ -28093,7 +28106,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="614" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" s="4">
         <v>45764</v>
       </c>
@@ -28134,7 +28147,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="615" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" s="4">
         <v>45761</v>
       </c>
@@ -28172,7 +28185,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="616" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" s="4">
         <v>45761</v>
       </c>
@@ -28213,7 +28226,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="617" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" s="4">
         <v>45761</v>
       </c>
@@ -28254,7 +28267,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="618" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" s="4">
         <v>45761</v>
       </c>
@@ -28295,7 +28308,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="619" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" s="4">
         <v>45758</v>
       </c>
@@ -28336,7 +28349,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="620" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" s="4">
         <v>45758</v>
       </c>
@@ -28380,7 +28393,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="621" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" s="4">
         <v>45757</v>
       </c>
@@ -28421,7 +28434,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="622" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" s="4">
         <v>45757</v>
       </c>
@@ -28459,7 +28472,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="623" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="4">
         <v>45756</v>
       </c>
@@ -28500,7 +28513,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="624" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="4">
         <v>45755</v>
       </c>
@@ -28541,7 +28554,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="625" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="4">
         <v>45754</v>
       </c>
@@ -28585,7 +28598,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="626" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="4">
         <v>45754</v>
       </c>
@@ -28626,7 +28639,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="627" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="4">
         <v>45754</v>
       </c>
@@ -28667,7 +28680,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="628" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="4">
         <v>45754</v>
       </c>
@@ -28708,7 +28721,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="629" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="4">
         <v>45754</v>
       </c>
@@ -28749,7 +28762,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="630" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="4">
         <v>45754</v>
       </c>
@@ -28790,7 +28803,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="631" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" s="4">
         <v>45754</v>
       </c>
@@ -28831,7 +28844,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="632" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" s="4">
         <v>45751</v>
       </c>
@@ -28872,7 +28885,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="633" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" s="4">
         <v>45751</v>
       </c>
@@ -28913,7 +28926,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="634" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" s="4">
         <v>45750</v>
       </c>
@@ -28954,7 +28967,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="635" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" s="4">
         <v>45750</v>
       </c>
@@ -28995,7 +29008,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="636" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" s="4">
         <v>45750</v>
       </c>
@@ -29039,7 +29052,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="637" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="4">
         <v>45748</v>
       </c>
@@ -29077,7 +29090,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="638" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="4">
         <v>45748</v>
       </c>
@@ -29121,7 +29134,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="639" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="4">
         <v>45748</v>
       </c>
@@ -29162,7 +29175,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="640" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="4">
         <v>45747</v>
       </c>
@@ -29200,7 +29213,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="641" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="4">
         <v>45747</v>
       </c>
@@ -29244,7 +29257,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="642" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="4">
         <v>45744</v>
       </c>
@@ -29296,7 +29309,7 @@
         <v>45732</v>
       </c>
       <c r="D643">
-        <v>2774.32</v>
+        <v>1000</v>
       </c>
       <c r="E643">
         <v>14132.12</v>
@@ -29323,7 +29336,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="644" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" s="4">
         <v>45741</v>
       </c>
@@ -29364,7 +29377,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="645" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" s="4">
         <v>45740</v>
       </c>
@@ -29405,7 +29418,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="646" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" s="4">
         <v>45736</v>
       </c>
@@ -29446,7 +29459,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="647" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" s="4">
         <v>45735</v>
       </c>
@@ -29487,7 +29500,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="648" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" s="4">
         <v>45733</v>
       </c>
@@ -29528,7 +29541,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="649" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" s="4">
         <v>45733</v>
       </c>
@@ -29569,7 +29582,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="650" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" s="4">
         <v>45733</v>
       </c>
@@ -29610,7 +29623,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="651" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" s="4">
         <v>45733</v>
       </c>
@@ -29651,7 +29664,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="652" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652" s="4">
         <v>45730</v>
       </c>
@@ -29695,7 +29708,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="653" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" s="4">
         <v>45730</v>
       </c>
@@ -29736,7 +29749,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="654" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" s="4">
         <v>45729</v>
       </c>
@@ -29777,7 +29790,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="655" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" s="4">
         <v>45728</v>
       </c>
@@ -29818,7 +29831,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="656" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656" s="4">
         <v>45728</v>
       </c>
@@ -29856,7 +29869,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="657" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657" s="4">
         <v>45727</v>
       </c>
@@ -29897,7 +29910,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="658" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658" s="4">
         <v>45727</v>
       </c>
@@ -29941,7 +29954,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="659" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659" s="4">
         <v>45727</v>
       </c>
@@ -29982,7 +29995,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="660" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" s="4">
         <v>45727</v>
       </c>
@@ -30023,7 +30036,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="661" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661" s="4">
         <v>45726</v>
       </c>
@@ -30064,7 +30077,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="662" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" s="4">
         <v>45726</v>
       </c>
@@ -30102,7 +30115,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="663" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" s="4">
         <v>45722</v>
       </c>
@@ -30146,7 +30159,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="664" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="4">
         <v>45721</v>
       </c>
@@ -30190,7 +30203,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="665" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="4">
         <v>45720</v>
       </c>
@@ -30231,7 +30244,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="666" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" s="4">
         <v>45720</v>
       </c>
@@ -30272,7 +30285,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="667" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667" s="4">
         <v>45719</v>
       </c>
@@ -30310,7 +30323,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="668" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" s="4">
         <v>45719</v>
       </c>
@@ -30351,7 +30364,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="669" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" s="4">
         <v>45719</v>
       </c>
@@ -30392,7 +30405,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="670" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670" s="4">
         <v>45716</v>
       </c>
@@ -30433,7 +30446,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="671" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" s="4">
         <v>45716</v>
       </c>
@@ -30477,7 +30490,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="672" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" s="4">
         <v>45715</v>
       </c>
@@ -30529,7 +30542,7 @@
         <v>45704</v>
       </c>
       <c r="D673">
-        <v>9215.2000000000007</v>
+        <v>1000</v>
       </c>
       <c r="E673">
         <v>19215.86</v>
@@ -30556,7 +30569,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="674" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" s="4">
         <v>45712</v>
       </c>
@@ -30597,7 +30610,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="675" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" s="4">
         <v>45712</v>
       </c>
@@ -30638,7 +30651,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="676" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" s="4">
         <v>45709</v>
       </c>
@@ -30679,7 +30692,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="677" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677" s="4">
         <v>45709</v>
       </c>
@@ -30720,7 +30733,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="678" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" s="4">
         <v>45709</v>
       </c>
@@ -30761,7 +30774,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="679" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" s="4">
         <v>45705</v>
       </c>
@@ -30802,7 +30815,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="680" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680" s="4">
         <v>45705</v>
       </c>
@@ -30843,7 +30856,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="681" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681" s="4">
         <v>45701</v>
       </c>
@@ -30884,7 +30897,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="682" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682" s="4">
         <v>45700</v>
       </c>
@@ -30925,7 +30938,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="683" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683" s="4">
         <v>45700</v>
       </c>
@@ -30966,7 +30979,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="684" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684" s="4">
         <v>45699</v>
       </c>
@@ -31010,7 +31023,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="685" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685" s="4">
         <v>45699</v>
       </c>
@@ -31051,7 +31064,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="686" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686" s="4">
         <v>45698</v>
       </c>
@@ -31092,7 +31105,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="687" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687" s="4">
         <v>45698</v>
       </c>
@@ -31133,7 +31146,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="688" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688" s="4">
         <v>45698</v>
       </c>
@@ -31174,7 +31187,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="689" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689" s="4">
         <v>45698</v>
       </c>
@@ -31212,7 +31225,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="690" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690" s="4">
         <v>45698</v>
       </c>
@@ -31253,7 +31266,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="691" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691" s="4">
         <v>45698</v>
       </c>
@@ -31294,7 +31307,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="692" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692" s="4">
         <v>45698</v>
       </c>
@@ -31335,7 +31348,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="693" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" s="4">
         <v>45698</v>
       </c>
@@ -31376,7 +31389,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="694" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694" s="4">
         <v>45698</v>
       </c>
@@ -31417,7 +31430,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="695" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695" s="4">
         <v>45698</v>
       </c>
@@ -31458,7 +31471,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="696" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696" s="4">
         <v>45698</v>
       </c>
@@ -31499,7 +31512,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="697" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697" s="4">
         <v>45695</v>
       </c>
@@ -31540,7 +31553,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="698" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698" s="4">
         <v>45694</v>
       </c>
@@ -31581,7 +31594,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="699" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699" s="4">
         <v>45694</v>
       </c>
@@ -31622,7 +31635,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="700" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" s="4">
         <v>45693</v>
       </c>
@@ -31666,7 +31679,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="701" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701" s="4">
         <v>45692</v>
       </c>
@@ -31707,7 +31720,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="702" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702" s="4">
         <v>45692</v>
       </c>
@@ -31748,7 +31761,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="703" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703" s="4">
         <v>45692</v>
       </c>
@@ -31789,7 +31802,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="704" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704" s="4">
         <v>45692</v>
       </c>
@@ -31830,7 +31843,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="705" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705" s="4">
         <v>45692</v>
       </c>
@@ -31871,7 +31884,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="706" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706" s="4">
         <v>45691</v>
       </c>
@@ -31909,7 +31922,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="707" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" s="4">
         <v>45691</v>
       </c>
@@ -31950,7 +31963,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="708" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708" s="4">
         <v>45691</v>
       </c>
@@ -31991,7 +32004,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="709" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709" s="4">
         <v>45691</v>
       </c>
@@ -32032,7 +32045,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="710" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710" s="4">
         <v>45691</v>
       </c>
@@ -32073,7 +32086,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="711" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711" s="4">
         <v>45691</v>
       </c>
@@ -32114,7 +32127,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="712" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712" s="4">
         <v>45691</v>
       </c>
@@ -32155,7 +32168,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="713" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713" s="4">
         <v>45688</v>
       </c>
@@ -32196,7 +32209,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="714" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714" s="4">
         <v>45688</v>
       </c>
@@ -32237,7 +32250,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="715" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715" s="4">
         <v>45688</v>
       </c>
@@ -32278,7 +32291,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="716" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716" s="4">
         <v>45688</v>
       </c>
@@ -32319,7 +32332,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="717" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717" s="4">
         <v>45688</v>
       </c>
@@ -32374,7 +32387,7 @@
         <v>45673</v>
       </c>
       <c r="D718">
-        <v>2583.7399999999998</v>
+        <v>1000</v>
       </c>
       <c r="E718">
         <v>15295.78</v>
@@ -32401,7 +32414,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="719" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719" s="4">
         <v>45686</v>
       </c>
@@ -32442,7 +32455,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="720" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720" s="4">
         <v>45685</v>
       </c>
@@ -32483,7 +32496,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="721" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A721" s="4">
         <v>45684</v>
       </c>
@@ -32524,7 +32537,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="722" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A722" s="4">
         <v>45684</v>
       </c>
@@ -32565,7 +32578,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="723" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A723" s="4">
         <v>45684</v>
       </c>
@@ -32606,7 +32619,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="724" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A724" s="4">
         <v>45681</v>
       </c>
@@ -32647,7 +32660,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="725" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A725" s="4">
         <v>45681</v>
       </c>
@@ -32688,7 +32701,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="726" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A726" s="4">
         <v>45681</v>
       </c>
@@ -32729,7 +32742,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="727" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A727" s="4">
         <v>45680</v>
       </c>
@@ -32770,7 +32783,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="728" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A728" s="4">
         <v>45680</v>
       </c>
@@ -32811,7 +32824,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="729" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A729" s="4">
         <v>45680</v>
       </c>
@@ -32852,7 +32865,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="730" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A730" s="4">
         <v>45679</v>
       </c>
@@ -32893,7 +32906,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="731" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A731" s="4">
         <v>45678</v>
       </c>
@@ -32934,7 +32947,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="732" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A732" s="4">
         <v>45678</v>
       </c>
@@ -32975,7 +32988,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="733" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A733" s="4">
         <v>45678</v>
       </c>
@@ -33016,7 +33029,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="734" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A734" s="4">
         <v>45677</v>
       </c>
@@ -33060,7 +33073,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="735" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A735" s="4">
         <v>45677</v>
       </c>
@@ -33101,7 +33114,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="736" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A736" s="4">
         <v>45677</v>
       </c>
@@ -33142,7 +33155,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="737" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A737" s="4">
         <v>45677</v>
       </c>
@@ -33183,7 +33196,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="738" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A738" s="4">
         <v>45674</v>
       </c>
@@ -33224,7 +33237,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="739" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A739" s="4">
         <v>45674</v>
       </c>
@@ -33265,7 +33278,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="740" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A740" s="4">
         <v>45674</v>
       </c>
@@ -33306,7 +33319,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="741" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A741" s="4">
         <v>45672</v>
       </c>
@@ -33344,7 +33357,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="742" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A742" s="4">
         <v>45672</v>
       </c>
@@ -33388,7 +33401,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="743" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A743" s="4">
         <v>45672</v>
       </c>
@@ -33429,7 +33442,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="744" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A744" s="4">
         <v>45671</v>
       </c>
@@ -33470,7 +33483,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="745" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A745" s="4">
         <v>45671</v>
       </c>
@@ -33511,7 +33524,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="746" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A746" s="4">
         <v>45671</v>
       </c>
@@ -33552,7 +33565,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="747" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A747" s="4">
         <v>45671</v>
       </c>
@@ -33593,7 +33606,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="748" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A748" s="4">
         <v>45670</v>
       </c>
@@ -33637,7 +33650,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="749" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A749" s="4">
         <v>45670</v>
       </c>
@@ -33678,7 +33691,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="750" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A750" s="4">
         <v>45670</v>
       </c>
@@ -33719,7 +33732,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="751" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A751" s="4">
         <v>45670</v>
       </c>
@@ -33760,7 +33773,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="752" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A752" s="4">
         <v>45667</v>
       </c>
@@ -33801,7 +33814,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="753" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A753" s="4">
         <v>45667</v>
       </c>
@@ -33845,7 +33858,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="754" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A754" s="4">
         <v>45667</v>
       </c>
@@ -33883,7 +33896,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="755" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A755" s="4">
         <v>45667</v>
       </c>
@@ -33927,7 +33940,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="756" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A756" s="4">
         <v>45666</v>
       </c>
@@ -33968,7 +33981,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="757" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A757" s="4">
         <v>45665</v>
       </c>
@@ -34009,7 +34022,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="758" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A758" s="4">
         <v>45664</v>
       </c>
@@ -34050,7 +34063,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="759" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A759" s="4">
         <v>45664</v>
       </c>
@@ -34094,7 +34107,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="760" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A760" s="4">
         <v>45664</v>
       </c>
@@ -34135,7 +34148,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="761" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A761" s="4">
         <v>45663</v>
       </c>
@@ -34179,7 +34192,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="762" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A762" s="4">
         <v>45664</v>
       </c>
@@ -34220,7 +34233,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="763" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A763" s="4">
         <v>45664</v>
       </c>
@@ -34261,7 +34274,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="764" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A764" s="4">
         <v>45664</v>
       </c>
@@ -34302,7 +34315,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="765" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A765" s="4">
         <v>45660</v>
       </c>
@@ -34343,7 +34356,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="766" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A766" s="4">
         <v>45659</v>
       </c>
@@ -34384,7 +34397,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="767" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A767" s="4">
         <v>45659</v>
       </c>
@@ -34422,7 +34435,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="768" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A768" s="4">
         <v>45659</v>
       </c>
@@ -34463,7 +34476,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="769" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A769" s="4">
         <v>45659</v>
       </c>
@@ -34504,7 +34517,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="770" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A770" s="4">
         <v>45659</v>
       </c>
@@ -34545,7 +34558,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="771" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A771" s="4">
         <v>45657</v>
       </c>
@@ -34583,7 +34596,17 @@
         <v>90</v>
       </c>
     </row>
+    <row r="775" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M775" s="5"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:N771" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="NOMINA"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
